--- a/AAII_Financials/Quarterly/LEA_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LEA_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>LEA</t>
   </si>
@@ -656,539 +656,551 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E7" s="2">
         <v>46116</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45927</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45836</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45745</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45563</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45472</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45381</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45108</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45017</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44835</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44744</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44653</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44471</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44380</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44289</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44107</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44016</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43925</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43736</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43645</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43554</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43372</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42917</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42826</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>6209400</v>
+      </c>
+      <c r="E8" s="3">
         <v>5822800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5988600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>5679800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6030400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>5560300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5714600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5584400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6012400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5994600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5841200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5781000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5999200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>5845500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5370900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5241200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>5071000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5208400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4879800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>4268200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>4760700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>5354400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>5243200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>4900100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2444500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4457700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4817600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>4825000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>5007600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>5160100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4942400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>4891600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>5580800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>5733700</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>5363800</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>4981500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>5123200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>4998500</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>4643500</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>4526400</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>5739100</v>
+      </c>
+      <c r="E9" s="3">
         <v>5337800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>5547900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>5316100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>5591300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>5125700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>5291900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>5179100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5563600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>5543900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>5391900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>5362800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5532600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5400400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>4926100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4848900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4706200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>4857400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4585500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4017200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>4349500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>4843400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4744600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>4423800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>2550600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>4095300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>4425800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>4340100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4494800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>4638300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>4397000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>4347500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>4934600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>5087400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>4769200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>4409400</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>4529800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>4408300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>4120600</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>3999300</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>470300</v>
+      </c>
+      <c r="E10" s="3">
         <v>485000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>440700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>363700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>439100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>434600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>422700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>405300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>448800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>450700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>449300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>418200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>466600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>445100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>444800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>392300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>364800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>351000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>294300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>251000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>411200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>511000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>498600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>476300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-106100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>362400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>391800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>484900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>512800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>521800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>545400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>544100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>646200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>646300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>594600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>572100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>593400</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>590200</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>522900</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>527100</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1231,19 +1243,20 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="3">
         <v>598700</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>8</v>
@@ -1251,11 +1264,11 @@
       <c r="H12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J12" s="3">
         <v>336800</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1263,11 +1276,11 @@
       <c r="L12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M12" s="3">
+      <c r="M12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N12" s="3">
         <v>319600</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1353,8 +1366,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1475,252 +1491,261 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>800</v>
+      </c>
+      <c r="E14" s="3">
         <v>42500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>111900</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I14" s="3">
         <v>88400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>55200</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>64900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>18800</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>16800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>75400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>18400</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>52300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>51300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>63300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>45400</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>19400</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>21700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>25500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>49100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>37600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>53700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>78200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>28100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>48800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>54300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>39200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>19800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>10000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>18400</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>24000</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>17000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>23100</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>8500</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>12700</v>
       </c>
-      <c r="AP14" s="3">
+      <c r="AQ14" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E15" s="3">
         <v>5000</v>
-      </c>
-      <c r="E15" s="3">
-        <v>4800</v>
       </c>
       <c r="F15" s="3">
         <v>4800</v>
       </c>
       <c r="G15" s="3">
+        <v>4800</v>
+      </c>
+      <c r="H15" s="3">
         <v>4700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>10600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>10700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>12700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>15100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>13200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>15500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>15000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>15900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>15300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>15200</v>
-      </c>
-      <c r="S15" s="3">
-        <v>15700</v>
       </c>
       <c r="T15" s="3">
         <v>15700</v>
       </c>
       <c r="U15" s="3">
+        <v>15700</v>
+      </c>
+      <c r="V15" s="3">
         <v>15900</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>15800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>16600</v>
-      </c>
-      <c r="X15" s="3">
-        <v>16500</v>
       </c>
       <c r="Y15" s="3">
         <v>16500</v>
       </c>
       <c r="Z15" s="3">
+        <v>16500</v>
+      </c>
+      <c r="AA15" s="3">
         <v>16300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>16000</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>17100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>17000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>16700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>15900</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>12700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>12500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>12700</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>13100</v>
       </c>
       <c r="AJ15" s="3">
         <v>13100</v>
       </c>
       <c r="AK15" s="3">
+        <v>13100</v>
+      </c>
+      <c r="AL15" s="3">
         <v>13500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>12500</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>11500</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>10100</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>11300</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>15200</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1760,252 +1785,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>5951500</v>
+      </c>
+      <c r="E17" s="3">
         <v>5532900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>5725300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>5486900</v>
       </c>
-      <c r="G17" s="3">
-        <v>5780200</v>
-      </c>
       <c r="H17" s="3">
+        <v>5788800</v>
+      </c>
+      <c r="I17" s="3">
         <v>5302200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>5476400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>5361600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5752100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5741700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5588600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>5566800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>5733600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>5600400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>5176900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>5049500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>4937800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5098600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4782500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4224800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4506600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>5049100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4950100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>4632900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2734600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>4307100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4662200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>4534000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4716200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>4852300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4603000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>4541500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>5116300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>5265200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4974700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>4574500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>4719900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4585500</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>4314900</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>4195500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>257900</v>
+      </c>
+      <c r="E18" s="3">
         <v>289900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>263300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>192900</v>
       </c>
-      <c r="G18" s="3">
-        <v>250200</v>
-      </c>
       <c r="H18" s="3">
+        <v>241600</v>
+      </c>
+      <c r="I18" s="3">
         <v>258100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>238200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>222800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>260300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>252900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>252600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>214200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>265600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>245100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>194000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>191700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>133200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>109800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>97300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>43400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>254100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>305300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>293100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>267200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-290100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>150600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>155400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>291000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>291400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>307800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>339400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>350100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>464500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>468500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>389100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>407000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>403300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>413000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>328600</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>330900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2048,89 +2080,90 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="E20" s="3">
         <v>-9300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3200</v>
       </c>
-      <c r="G20" s="3">
-        <v>-8700</v>
-      </c>
       <c r="H20" s="3">
+        <v>-20300</v>
+      </c>
+      <c r="I20" s="3">
         <v>-3800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-15500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-6800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>19100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-10600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>3300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-12000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-3500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-8600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-11200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-6900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-4200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-17700</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
         <v>0</v>
       </c>
@@ -2170,496 +2203,511 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>290100</v>
+      </c>
+      <c r="E21" s="3">
         <v>304200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>266100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>200900</v>
       </c>
-      <c r="G21" s="3">
-        <v>263600</v>
-      </c>
       <c r="H21" s="3">
+        <v>266600</v>
+      </c>
+      <c r="I21" s="3">
         <v>267100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>264300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>240300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>280200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>273500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>246700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>240300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>280500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>265900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>339500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>319000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>281300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>244600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>228600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>176900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>401800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>441900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>438200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>398000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-160800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>263400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>284900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>419500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>419700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>431400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>462000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>469900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>586300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>588700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>503600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>518700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>507900</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>509900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>423400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>429600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>24200</v>
+      </c>
+      <c r="E22" s="3">
         <v>25600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>25000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>24600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>25400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>25800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>26700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>26500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>26900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>26100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>25700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>26200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>24200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>24000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>24800</v>
-      </c>
-      <c r="S22" s="3">
-        <v>24900</v>
       </c>
       <c r="T22" s="3">
         <v>24900</v>
       </c>
       <c r="U22" s="3">
+        <v>24900</v>
+      </c>
+      <c r="V22" s="3">
         <v>24600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>22600</v>
-      </c>
-      <c r="W22" s="3">
-        <v>22300</v>
       </c>
       <c r="X22" s="3">
         <v>22300</v>
       </c>
       <c r="Y22" s="3">
+        <v>22300</v>
+      </c>
+      <c r="Z22" s="3">
         <v>21500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>26500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>27200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>24400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>22600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>24000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>24500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>20900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>21300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>21200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>20900</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>20700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>21800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>21700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>21400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>20800</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>20500</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>20600</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>260200</v>
+      </c>
+      <c r="E23" s="3">
         <v>231100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>124400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>171500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>233500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>147700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>171800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>203100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>240600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>167400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>189700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>199100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>228700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>209000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>173300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>154900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>104800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>76300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>61500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>13900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>229300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>278800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>273900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>235200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-318300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>108500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>132800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>267000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>266900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>286900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>318100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>328900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>443600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>447800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>367300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>385300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>381900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>392200</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>308100</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>310300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>48500</v>
+      </c>
+      <c r="E24" s="3">
         <v>38400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>18100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>45100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>41600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>45200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>57300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>47100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>46200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>40500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>46700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>47000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>41500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>45600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>48100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>41700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>23500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>20400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>18600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>20900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>39300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>58900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>63800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>44600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-41000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>26500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>33500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>73300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>43100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>74900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>64500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>98800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>79000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>103700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>77800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>73300</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>89100</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>82800</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>88200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2780,252 +2828,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>211700</v>
+      </c>
+      <c r="E26" s="3">
         <v>192700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>106300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>126400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>191900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>102500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>114500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>156000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>194400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>126900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>143000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>152100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>187200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>163400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>125200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>113200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>81300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>55900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>42900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>190000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>219900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>210100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>190600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-277300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>82000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>136600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>233500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>193600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>243800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>243200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>264400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>344800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>368800</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>263600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>307500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>308600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>303100</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>225300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>222100</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>192800</v>
+      </c>
+      <c r="E27" s="3">
         <v>172300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>82700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>108200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>165200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>80700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>88100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>135800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>173100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>109600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>127300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>132900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>168700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>143600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>117500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>92300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>68500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>49400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>21500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-26500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>175200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>203700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>201600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>174400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-293900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>76400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>126000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>215900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>182800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>228900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>216200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>245600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>330300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>352400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>254100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>295200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>311900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>305800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>229900</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3146,8 +3203,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3220,8 +3280,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -3238,23 +3298,23 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-4000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>6900</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>1100</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>1300</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>146400</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
@@ -3268,8 +3328,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3390,8 +3453,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3512,89 +3578,92 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E32" s="3">
         <v>9300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3200</v>
       </c>
-      <c r="G32" s="3">
-        <v>8700</v>
-      </c>
       <c r="H32" s="3">
+        <v>20300</v>
+      </c>
+      <c r="I32" s="3">
         <v>3800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>15500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>6800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-19100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>10600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-3300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>12000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>3500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>8600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>11200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>6900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>4200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>17700</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
         <v>0</v>
       </c>
@@ -3634,130 +3703,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>192800</v>
+      </c>
+      <c r="E33" s="3">
         <v>172300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>82700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>108200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>165200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>80700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>88100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>135800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>173100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>109600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>127300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>132900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>168700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>143600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>117500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>92300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>68500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>49400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>21500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-26500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>175200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>203700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>201600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>174400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-293900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>76400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>126000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>215900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>182800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>228900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>212200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>252500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>331400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>353700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>400500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>295200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>311900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>305800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>229900</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3878,257 +3953,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>192800</v>
+      </c>
+      <c r="E35" s="3">
         <v>172300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>82700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>108200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>165200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>80700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>88100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>135800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>173100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>109600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>127300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>132900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>168700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>143600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>117500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>92300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>68500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>49400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>21500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-26500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>175200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>203700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>201600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>174400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-293900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>76400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>126000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>215900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>182800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>228900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>212200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>252500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>331400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>353700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>400500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>295200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>311900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>305800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>229900</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E38" s="2">
         <v>46116</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45927</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45836</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45745</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45563</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45472</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45381</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45108</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45017</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44835</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44744</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44653</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44471</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44380</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44289</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44107</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44016</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43925</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43736</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43645</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43554</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43372</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42917</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42826</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4171,8 +4255,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4215,219 +4300,223 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1000600</v>
+      </c>
+      <c r="E41" s="3">
         <v>881900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1033000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1009600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>887900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>779900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1052900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>763900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>950300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>930400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1196300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>979700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>901900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>898500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1114900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>842200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>828000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1162000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1318300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1099100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1401700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1375400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1306700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1250400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1775500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2449100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1487700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1300900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1269000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1199400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1493200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1198600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1327900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1268500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1500400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1253700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1166700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1209700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1271600</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1341600</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E42" s="3">
         <v>5000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>10100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10200</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>7200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5400</v>
-      </c>
-      <c r="I42" s="3">
-        <v>6600</v>
       </c>
       <c r="J42" s="3">
         <v>6600</v>
       </c>
       <c r="K42" s="3">
+        <v>6600</v>
+      </c>
+      <c r="L42" s="3">
         <v>6200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>4800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>1700</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>1800</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>1100</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>3600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>3400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>3300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1800</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>3500</v>
-      </c>
-      <c r="V42" s="3">
-        <v>2700</v>
       </c>
       <c r="W42" s="3">
         <v>2700</v>
       </c>
       <c r="X42" s="3">
+        <v>2700</v>
+      </c>
+      <c r="Y42" s="3">
         <v>2600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>9300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>8900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>7600</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>7700</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
-      </c>
       <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="3">
         <v>16100</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>15700</v>
-      </c>
-      <c r="AF42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG42" s="3" t="s">
         <v>8</v>
@@ -4438,8 +4527,8 @@
       <c r="AI42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ42" s="3">
-        <v>0</v>
+      <c r="AJ42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK42" s="3">
         <v>0</v>
@@ -4459,585 +4548,600 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4416700</v>
+      </c>
+      <c r="E43" s="3">
         <v>4383600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4093600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4441500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4836800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4495500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3837600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4600500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4419200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4409900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3901400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>4276900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>4478200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>4347400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3451900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3570300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3369700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>3236100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>3041500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2865100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2965000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3441300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>3269200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>3386800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2354900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2472100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>2982600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3320700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3467700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3468800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>2880300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>3301800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>3440100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>3795200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>3230800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>3357900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>3357700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>3308800</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>2746500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>3109500</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1723900</v>
+      </c>
+      <c r="E44" s="3">
         <v>1750700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1693200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1762800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1684000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1681500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1601100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1768100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1702400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1735400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1758000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1788300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1702600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1676200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1573600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1594100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1612800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1642100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1571900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1766000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1590300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1464800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1401100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1265600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1245400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1324300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1258200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1294100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1240300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1200500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1196800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1285200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1248800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1266300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1205700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1232900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1127400</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1067800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1020600</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>1063000</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1236100</v>
+      </c>
+      <c r="E45" s="3">
         <v>1230600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>832200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>805800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>794100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>751200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>685100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>667300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>700900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>826600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>775800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>689200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>745700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>654800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>850100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>914700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>871600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>886500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>830000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>861100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>894600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>756700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>790400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>686800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>665500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>655300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>678200</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>686200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>743600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>728900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>710200</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>782100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>812000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>769700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>676100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>718500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>690100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>642600</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>610600</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>539700</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>8385400</v>
+      </c>
+      <c r="E46" s="3">
         <v>8254000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>7663000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8033100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8215400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>7715800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>7184100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>7808500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>7780800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>7907700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>7636900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>7737700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7831600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7578600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6994100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>6924700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>6685400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>6928500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>6765200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>6594000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>6854300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>7040800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>6776700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>6598500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>6048900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>6908500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6406700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>6618000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>6736300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>6597600</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>6280500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>6567700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>6828800</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>7099700</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>6613000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>6563000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>6341900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>6228900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>5649300</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>6053800</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>110200</v>
+      </c>
+      <c r="E47" s="3">
         <v>103300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>105000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>104100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>99200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>93200</v>
-      </c>
-      <c r="I47" s="3">
-        <v>93800</v>
       </c>
       <c r="J47" s="3">
         <v>93800</v>
       </c>
       <c r="K47" s="3">
+        <v>93800</v>
+      </c>
+      <c r="L47" s="3">
         <v>85300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>84600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>79700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>75800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>75400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>72900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>53600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>48100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>48600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>56500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>58800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>55100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>53700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>50100</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>49400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>41900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>39700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>33200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>42100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>39500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>38200</v>
-      </c>
-      <c r="AF47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG47" s="3" t="s">
         <v>8</v>
@@ -5048,8 +5152,8 @@
       <c r="AI47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ47" s="3">
-        <v>0</v>
+      <c r="AJ47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK47" s="3">
         <v>0</v>
@@ -5069,252 +5173,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3596900</v>
+      </c>
+      <c r="E48" s="3">
         <v>3588100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3635500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3617300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3641600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3555800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3533200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3651700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3585200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3643600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3710900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3617900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3638100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3565200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>3555800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>3357200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>3435100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>3503900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>3348000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>3310600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>3257100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>3244400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>3276500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>3166700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>3155500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>3120500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3231200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3113700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3068200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3036800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>2598100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2536200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>2516500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>2560900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2459400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2378100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>2266700</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>2070700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>2019300</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>1920900</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1777100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1775800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1777800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1761800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1761100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1723200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1699200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1754400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1720400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1719900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1737900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1714100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1735800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1666700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1896000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1604800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1651900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1675300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1960400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1660400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1667400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1657700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1655800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1629000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1606100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1592200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>2038000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1600400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1600200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1406300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1801800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1409400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1421400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1464700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1845400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1387100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1272100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1129400</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1408400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>1069400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5435,8 +5548,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5557,130 +5673,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>1780900</v>
+      </c>
+      <c r="E52" s="3">
         <v>1732400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1661800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1641400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1604800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1535300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>1517200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>1509700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1510200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1516200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1530100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1468200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1517600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1520800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1263500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1444400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1524400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1563100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1220000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1425900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1431200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1429500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1440200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1458600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1418800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1367900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>962700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1381700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1404800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1321300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>920300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1496100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1515700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1555900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1028100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1383800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1356500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1171500</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>823600</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>1233300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5801,130 +5923,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15650500</v>
+      </c>
+      <c r="E54" s="3">
         <v>15453600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14843100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15157700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15322100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14623300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14027500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14818100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14681900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14872000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14695500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14613700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14798500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14404200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13763000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13379200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13345400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13727300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13352400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13046000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13263700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13422500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13198600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12894700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12269000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13022300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12680700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12753300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12847700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12362000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11600700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12009400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12282400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12681200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>11945900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>11712000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>11237200</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>10600500</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>9900600</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>10277400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5967,8 +6095,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6011,263 +6140,270 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>3931000</v>
+      </c>
+      <c r="E57" s="3">
         <v>3780200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3285200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3619100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3748900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3631600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>3092100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>3493700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>3552200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>3688700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>3301100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3556500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3641300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3578900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>3206100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>3278000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>3110700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>3209800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>2952400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>2870000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2886500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>3132700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>3141600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2943400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>1902600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>2496500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>2821700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2986800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3060800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3094400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2862800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>3041800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>3268800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>3483000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>3167200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>3176000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>3202900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>3043000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>2640500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>2773200</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>205300</v>
+      </c>
+      <c r="E58" s="3">
         <v>201700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>201000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>197800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>197600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>187900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>181500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>194100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>180100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>181700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>179700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>176200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>176800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>166500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>20700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>5100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>700</v>
-      </c>
-      <c r="T58" s="3">
-        <v>800</v>
       </c>
       <c r="U58" s="3">
         <v>800</v>
       </c>
       <c r="V58" s="3">
+        <v>800</v>
+      </c>
+      <c r="W58" s="3">
         <v>206000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>9500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>14200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>23300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1024300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1025300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>33300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>35800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>29300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>28700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>22800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>17200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>11700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>12000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>9000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>10800</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>45900</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>49000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>44200</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>41300</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E59" s="3">
+      <c r="E59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="3">
         <v>560300</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>8</v>
@@ -6275,11 +6411,11 @@
       <c r="H59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>594100</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>8</v>
@@ -6287,11 +6423,11 @@
       <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M59" s="3">
+      <c r="M59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N59" s="3">
         <v>622500</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O59" s="3" t="s">
         <v>8</v>
@@ -6299,452 +6435,464 @@
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R59" s="3">
         <v>1961500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1906700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1916200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1876500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1806700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1875500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1984100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2031100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1920900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2087800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1859900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1826700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1811200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1885200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1936900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1791300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>1615000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>1720900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>1769600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>1801400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>1678100</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>1706200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>1693500</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>1538700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>1497600</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>1668800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6382200</v>
+      </c>
+      <c r="E60" s="3">
         <v>6215800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>5667100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>5949600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>6122200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>5847300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>5447000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5892700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>5817800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>5943000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>5667200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>5701400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5775200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5597600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5188300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>5189800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>5027600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>5087100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>4759900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>4951500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>4875400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>5173300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>5076700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>5054500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>4786800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>5348500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>4666200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>4907800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>5027000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>4914400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>4500600</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>4779900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>5050100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>5296400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>4854300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>4893000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>4942300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>4630700</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>4182300</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>4483300</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3310400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3322700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3306400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3350100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3353500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3319800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3315800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3380300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3350800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3361700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3365600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3362800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3359000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3200800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2591200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2600500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2595200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2595800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2595200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2095800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2301300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2300800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2300300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2299800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2302700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2306800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2293700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2297600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2300100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1938600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1941000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1946600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1948200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1950000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1951500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1953000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1877100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1889000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1898000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>1907300</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>633200</v>
+      </c>
+      <c r="E62" s="3">
         <v>639800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>495800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>615500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>635700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>631600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>501800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>650800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>599300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>581100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>419300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>566200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>573000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>576400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1153200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1161000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1174700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1218500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1188900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1241200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1194900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1199700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1206700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1145000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1082000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1070200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1101300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1026300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>966100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>958700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>640400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>685600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>689200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>709900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>694100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>691000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>661600</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>617300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>627400</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>643800</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6865,8 +7013,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6987,8 +7138,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7109,130 +7263,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10325800</v>
+      </c>
+      <c r="E66" s="3">
         <v>10178300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9642100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9915200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10111400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9798700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>9426500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9923800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9767900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>9885800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9634900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9630400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9707200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9374800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9084200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9075900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>8904800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9077300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>8709000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>8423600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>8480800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>8842400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8731300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8761900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8401300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8998800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>8331000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>8549500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8611300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>8116700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7400000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>7716500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>7982500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>8281800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>7795400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>7840900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>7615300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>7269500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>6843400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>7198900</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7275,8 +7435,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7397,8 +7558,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7519,8 +7683,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7641,8 +7808,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7763,130 +7933,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6473100</v>
+      </c>
+      <c r="E72" s="3">
         <v>6320500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6189000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6147200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6081600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>5959300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>5931000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5884400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5793200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5664800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5601100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5519300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5432300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5310000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>5214100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>5143000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>5097100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>5075400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>5072800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>5098100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>5155100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4995200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4806800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4620700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4447100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4741800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4715800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4608400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4435300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4300300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4113600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4953800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4750000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4474800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4171900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>3810300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>3572600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4031400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>3706900</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>3503300</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8007,8 +8183,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8129,8 +8308,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8251,130 +8433,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5180700</v>
+      </c>
+      <c r="E76" s="3">
         <v>5086600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5035100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5105800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5082000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4658400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4451700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4765200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4801800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4892900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4918800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4858800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4980500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4857700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4678800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4303300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4440600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4650000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4643400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4622400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4782900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4580100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4467300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4132800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3867700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4023500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4349700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4203800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4236400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4245300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4200700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>4292900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4299900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>4399400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4150500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3871100</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3621900</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3331000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3057200</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>3078500</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8495,257 +8683,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46207</v>
+      </c>
+      <c r="E80" s="2">
         <v>46116</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45927</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45836</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45745</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45563</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45472</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45381</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45108</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45017</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44835</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44744</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44653</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44471</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44380</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44289</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44107</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44016</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43925</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43736</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43645</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43554</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43372</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42917</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42826</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>192800</v>
+      </c>
+      <c r="E81" s="3">
         <v>172300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>82700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>108200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>165200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>80700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>88100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>135800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>173100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>109600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>127300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>132900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>168700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>143600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>117500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>92300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>68500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>49400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>21500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-26500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>175200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>203700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>201600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>174400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-293900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>76400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>126000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>215900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>182800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>228900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>212200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>252500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>331400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>353700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>400500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>295200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>311900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>305800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>229900</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>214400</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8788,130 +8985,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>143500</v>
+      </c>
+      <c r="E83" s="3">
         <v>142500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>148500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>141700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>141200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>140200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>139000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>136400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>135200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>131300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>126900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>124100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>127000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>127700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>142200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>139300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>151600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>143400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>142500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>140400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>150200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>140800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>142800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>136300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>130300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>130500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>129500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>128500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>128300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>123600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>122600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>119800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>121800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>120200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>114500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>111700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>104600</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>96900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>94800</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>98700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9032,8 +9233,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9154,8 +9358,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9276,8 +9483,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9398,8 +9608,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9520,130 +9733,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>460500</v>
+      </c>
+      <c r="E89" s="3">
         <v>98100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>475900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>444400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>296200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-127700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>680800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>182700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>291200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-34600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>569700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>403800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>311400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-35600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>537200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>252100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>11400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>220700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>166900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-4400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>260100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>247500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>400800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>564500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-524500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>222300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>485000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>343400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>404300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>51600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>758200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>267900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>516900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>236800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>598800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>339000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>566400</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>278900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>525400</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>276300</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9686,130 +9905,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-172700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-124600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-194800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-137400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-125400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-104000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-192100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-132200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-120800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-113600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-193200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-153200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-168300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-111800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-195300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-140400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-172200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-130300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-179600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-152600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-140000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-112900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-167000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-90100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-86100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-109100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-193800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-150800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-136500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-122800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-184300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-160500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-169400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-162800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-164300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-156200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-153200</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-120800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-228000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-118600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9930,8 +10153,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10052,130 +10278,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-162400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-118700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-191200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-135800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-122800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-67000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-175100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-138000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-119000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-110900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-158400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-153200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-340400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-109500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-213600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-131800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-182300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-302600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-168900</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-194600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-140300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-142900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-171700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-121100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-85900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-90100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-183100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-159200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-463500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-116600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-182300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-153900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-169200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-188100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-168500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-133800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-437600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-128700</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-388600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-117300</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10218,130 +10450,134 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E96" s="3">
         <v>42500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>39400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>40900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>41200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>43300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>41800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>42800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>43600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>45500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>44600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>45200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>45300</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>46800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-46100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-45900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-46100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-47400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-46000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-29900</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-15100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-15700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-15300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-4100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-47800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-45200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-45500</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-46100</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-49500</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-44200</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-45400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-46000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-50700</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-33300</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-33700</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-34000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-36700</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-20700</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-21100</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10462,8 +10698,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10584,8 +10823,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10706,370 +10948,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-182400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-137600</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-269700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-189400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-75400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-84000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-187600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-255300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-147100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-103900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-211700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-159900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>34600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-82500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-74100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-91700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-150300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-71200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>218400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-99700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-102600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-29700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-199900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1013100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-49300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>850600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-125400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-131200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>129400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-234700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-277300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-246100</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-234500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-272600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-196200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-128900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-191600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-225300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-173500</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-215500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E101" s="3">
         <v>6000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-30400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>24700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-3900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-16700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>15700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-12800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>11000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>23600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-15200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-12700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>23600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-15200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-12700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>9000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-10900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>27100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>14800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>10900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-31300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>10600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-20600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-9800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-40900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>18000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>12600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>10700</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>19800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>13200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-33300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>3400</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>119600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-150800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>20900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>121100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>110600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-272700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>287700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-185900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>21200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-266100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>215300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>77900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-216600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>273100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>13400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-333900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-156500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>219200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-302600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>26200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>64000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>56300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-554900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-648800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>951500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>187100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>32400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>70000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-298900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>294900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-141900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>72300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-205900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>246700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>87000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-43000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-61900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-70000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-53100</v>
       </c>
     </row>
